--- a/www/flightdata/xlsx/eoss-396.xlsx
+++ b/www/flightdata/xlsx/eoss-396.xlsx
@@ -2640,7 +2640,7 @@
         <v>46131.29394607639</v>
       </c>
       <c r="D2" s="1">
-        <v>46131.54392361111</v>
+        <v>46131.29392361111</v>
       </c>
       <c r="E2">
         <v>5214</v>
@@ -2747,7 +2747,7 @@
         <v>46131.29461106481</v>
       </c>
       <c r="D3" s="1">
-        <v>46131.54454861111</v>
+        <v>46131.29454861111</v>
       </c>
       <c r="E3">
         <v>5738</v>
@@ -2878,7 +2878,7 @@
         <v>46131.29463773148</v>
       </c>
       <c r="D4" s="1">
-        <v>46131.54461805556</v>
+        <v>46131.29461805556</v>
       </c>
       <c r="E4">
         <v>5903</v>
@@ -3021,7 +3021,7 @@
         <v>46131.294935590275</v>
       </c>
       <c r="D5" s="1">
-        <v>46131.544895833336</v>
+        <v>46131.294895833336</v>
       </c>
       <c r="E5">
         <v>6351</v>
@@ -3164,7 +3164,7 @@
         <v>46131.29499342592</v>
       </c>
       <c r="D6" s="1">
-        <v>46131.544965277775</v>
+        <v>46131.294965277775</v>
       </c>
       <c r="E6">
         <v>6534</v>
@@ -3307,7 +3307,7 @@
         <v>46131.2953058912</v>
       </c>
       <c r="D7" s="1">
-        <v>46131.54524305555</v>
+        <v>46131.29524305555</v>
       </c>
       <c r="E7">
         <v>6984</v>
@@ -3450,7 +3450,7 @@
         <v>46131.29534076389</v>
       </c>
       <c r="D8" s="1">
-        <v>46131.5453125</v>
+        <v>46131.2953125</v>
       </c>
       <c r="E8">
         <v>7168</v>
@@ -3593,7 +3593,7 @@
         <v>46131.295630092594</v>
       </c>
       <c r="D9" s="1">
-        <v>46131.545590277776</v>
+        <v>46131.295590277776</v>
       </c>
       <c r="E9">
         <v>7613</v>
@@ -3736,7 +3736,7 @@
         <v>46131.295687743055</v>
       </c>
       <c r="D10" s="1">
-        <v>46131.54565972222</v>
+        <v>46131.29565972222</v>
       </c>
       <c r="E10">
         <v>7803</v>
@@ -3879,7 +3879,7 @@
         <v>46131.296000497685</v>
       </c>
       <c r="D11" s="1">
-        <v>46131.5459375</v>
+        <v>46131.2959375</v>
       </c>
       <c r="E11">
         <v>8270</v>
@@ -4022,7 +4022,7 @@
         <v>46131.2960271875</v>
       </c>
       <c r="D12" s="1">
-        <v>46131.546006944445</v>
+        <v>46131.296006944445</v>
       </c>
       <c r="E12">
         <v>8461</v>
@@ -4165,7 +4165,7 @@
         <v>46131.29634804398</v>
       </c>
       <c r="D13" s="1">
-        <v>46131.54628472222</v>
+        <v>46131.29628472222</v>
       </c>
       <c r="E13">
         <v>8918</v>
@@ -4308,7 +4308,7 @@
         <v>46131.296373958336</v>
       </c>
       <c r="D14" s="1">
-        <v>46131.54635416667</v>
+        <v>46131.29635416667</v>
       </c>
       <c r="E14">
         <v>9111</v>
@@ -4451,7 +4451,7 @@
         <v>46131.29670679398</v>
       </c>
       <c r="D15" s="1">
-        <v>46131.546631944446</v>
+        <v>46131.296631944446</v>
       </c>
       <c r="E15">
         <v>9581</v>
@@ -4594,7 +4594,7 @@
         <v>46131.296730775466</v>
       </c>
       <c r="D16" s="1">
-        <v>46131.54670138889</v>
+        <v>46131.29670138889</v>
       </c>
       <c r="E16">
         <v>9770</v>
@@ -4737,7 +4737,7 @@
         <v>46131.297019895836</v>
       </c>
       <c r="D17" s="1">
-        <v>46131.54697916667</v>
+        <v>46131.29697916667</v>
       </c>
       <c r="E17">
         <v>10231</v>
@@ -4880,7 +4880,7 @@
         <v>46131.297068391206</v>
       </c>
       <c r="D18" s="1">
-        <v>46131.54704861111</v>
+        <v>46131.29704861111</v>
       </c>
       <c r="E18">
         <v>10418</v>
@@ -5023,7 +5023,7 @@
         <v>46131.2974253125</v>
       </c>
       <c r="D19" s="1">
-        <v>46131.54739583333</v>
+        <v>46131.29739583333</v>
       </c>
       <c r="E19">
         <v>11062</v>
@@ -5166,7 +5166,7 @@
         <v>46131.29776270833</v>
       </c>
       <c r="D20" s="1">
-        <v>46131.547743055555</v>
+        <v>46131.297743055555</v>
       </c>
       <c r="E20">
         <v>11709</v>
@@ -5309,7 +5309,7 @@
         <v>46131.29811001157</v>
       </c>
       <c r="D21" s="1">
-        <v>46131.54809027778</v>
+        <v>46131.29809027778</v>
       </c>
       <c r="E21">
         <v>12390</v>
@@ -5452,7 +5452,7 @@
         <v>46131.29841004629</v>
       </c>
       <c r="D22" s="1">
-        <v>46131.548368055555</v>
+        <v>46131.298368055555</v>
       </c>
       <c r="E22">
         <v>12876</v>
@@ -5595,7 +5595,7 @@
         <v>46131.298456805554</v>
       </c>
       <c r="D23" s="1">
-        <v>46131.5484375</v>
+        <v>46131.2984375</v>
       </c>
       <c r="E23">
         <v>13075</v>
@@ -5738,7 +5738,7 @@
         <v>46131.298780034725</v>
       </c>
       <c r="D24" s="1">
-        <v>46131.54871527778</v>
+        <v>46131.29871527778</v>
       </c>
       <c r="E24">
         <v>13565</v>
@@ -5881,7 +5881,7 @@
         <v>46131.29880481482</v>
       </c>
       <c r="D25" s="1">
-        <v>46131.548784722225</v>
+        <v>46131.298784722225</v>
       </c>
       <c r="E25">
         <v>13754</v>
@@ -6024,7 +6024,7 @@
         <v>46131.29915125</v>
       </c>
       <c r="D26" s="1">
-        <v>46131.54913194444</v>
+        <v>46131.29913194444</v>
       </c>
       <c r="E26">
         <v>14430</v>
@@ -6167,7 +6167,7 @@
         <v>46131.29949855324</v>
       </c>
       <c r="D27" s="1">
-        <v>46131.549479166664</v>
+        <v>46131.299479166664</v>
       </c>
       <c r="E27">
         <v>15163</v>
@@ -6310,7 +6310,7 @@
         <v>46131.29984633102</v>
       </c>
       <c r="D28" s="1">
-        <v>46131.54982638889</v>
+        <v>46131.29982638889</v>
       </c>
       <c r="E28">
         <v>15828</v>
@@ -6453,7 +6453,7 @@
         <v>46131.300193333336</v>
       </c>
       <c r="D29" s="1">
-        <v>46131.55017361111</v>
+        <v>46131.30017361111</v>
       </c>
       <c r="E29">
         <v>16553</v>
@@ -6596,7 +6596,7 @@
         <v>46131.30054094907</v>
       </c>
       <c r="D30" s="1">
-        <v>46131.550520833334</v>
+        <v>46131.300520833334</v>
       </c>
       <c r="E30">
         <v>17252</v>
@@ -6739,7 +6739,7 @@
         <v>46131.30088744213</v>
       </c>
       <c r="D31" s="1">
-        <v>46131.55086805556</v>
+        <v>46131.30086805556</v>
       </c>
       <c r="E31">
         <v>17909</v>
@@ -6882,7 +6882,7 @@
         <v>46131.301234976854</v>
       </c>
       <c r="D32" s="1">
-        <v>46131.55121527778</v>
+        <v>46131.30121527778</v>
       </c>
       <c r="E32">
         <v>18588</v>
@@ -7025,7 +7025,7 @@
         <v>46131.301595034725</v>
       </c>
       <c r="D33" s="1">
-        <v>46131.5515625</v>
+        <v>46131.3015625</v>
       </c>
       <c r="E33">
         <v>19243</v>
@@ -7168,7 +7168,7 @@
         <v>46131.30192893519</v>
       </c>
       <c r="D34" s="1">
-        <v>46131.55190972222</v>
+        <v>46131.30190972222</v>
       </c>
       <c r="E34">
         <v>19929</v>
@@ -7311,7 +7311,7 @@
         <v>46131.302276319446</v>
       </c>
       <c r="D35" s="1">
-        <v>46131.552256944444</v>
+        <v>46131.302256944444</v>
       </c>
       <c r="E35">
         <v>20601</v>
@@ -7454,7 +7454,7 @@
         <v>46131.30262390046</v>
       </c>
       <c r="D36" s="1">
-        <v>46131.55260416667</v>
+        <v>46131.30260416667</v>
       </c>
       <c r="E36">
         <v>21347</v>
@@ -7597,7 +7597,7 @@
         <v>46131.302984444446</v>
       </c>
       <c r="D37" s="1">
-        <v>46131.55295138889</v>
+        <v>46131.30295138889</v>
       </c>
       <c r="E37">
         <v>22038</v>
@@ -7740,7 +7740,7 @@
         <v>46131.30331859954</v>
       </c>
       <c r="D38" s="1">
-        <v>46131.553298611114</v>
+        <v>46131.303298611114</v>
       </c>
       <c r="E38">
         <v>22733</v>
@@ -7883,7 +7883,7 @@
         <v>46131.303665775464</v>
       </c>
       <c r="D39" s="1">
-        <v>46131.55364583333</v>
+        <v>46131.30364583333</v>
       </c>
       <c r="E39">
         <v>23511</v>
@@ -8026,7 +8026,7 @@
         <v>46131.30401273148</v>
       </c>
       <c r="D40" s="1">
-        <v>46131.55399305555</v>
+        <v>46131.30399305555</v>
       </c>
       <c r="E40">
         <v>24243</v>
@@ -8169,7 +8169,7 @@
         <v>46131.30435953704</v>
       </c>
       <c r="D41" s="1">
-        <v>46131.55434027778</v>
+        <v>46131.30434027778</v>
       </c>
       <c r="E41">
         <v>24981</v>
@@ -8312,7 +8312,7 @@
         <v>46131.304721319444</v>
       </c>
       <c r="D42" s="1">
-        <v>46131.5546875</v>
+        <v>46131.3046875</v>
       </c>
       <c r="E42">
         <v>25698</v>
@@ -8455,7 +8455,7 @@
         <v>46131.30505408565</v>
       </c>
       <c r="D43" s="1">
-        <v>46131.55503472222</v>
+        <v>46131.30503472222</v>
       </c>
       <c r="E43">
         <v>26417</v>
@@ -8598,7 +8598,7 @@
         <v>46131.30540142361</v>
       </c>
       <c r="D44" s="1">
-        <v>46131.55538194445</v>
+        <v>46131.30538194445</v>
       </c>
       <c r="E44">
         <v>27078</v>
@@ -8741,7 +8741,7 @@
         <v>46131.305748784725</v>
       </c>
       <c r="D45" s="1">
-        <v>46131.55572916667</v>
+        <v>46131.30572916667</v>
       </c>
       <c r="E45">
         <v>27742</v>
@@ -8884,7 +8884,7 @@
         <v>46131.30609599537</v>
       </c>
       <c r="D46" s="1">
-        <v>46131.556076388886</v>
+        <v>46131.306076388886</v>
       </c>
       <c r="E46">
         <v>28346</v>
@@ -9027,7 +9027,7 @@
         <v>46131.306443194444</v>
       </c>
       <c r="D47" s="1">
-        <v>46131.55642361111</v>
+        <v>46131.30642361111</v>
       </c>
       <c r="E47">
         <v>28932</v>
@@ -9170,7 +9170,7 @@
         <v>46131.30679056713</v>
       </c>
       <c r="D48" s="1">
-        <v>46131.55677083333</v>
+        <v>46131.30677083333</v>
       </c>
       <c r="E48">
         <v>29504</v>
@@ -9313,7 +9313,7 @@
         <v>46131.307137523145</v>
       </c>
       <c r="D49" s="1">
-        <v>46131.557118055556</v>
+        <v>46131.307118055556</v>
       </c>
       <c r="E49">
         <v>30136</v>
@@ -9456,7 +9456,7 @@
         <v>46131.30748506945</v>
       </c>
       <c r="D50" s="1">
-        <v>46131.55746527778</v>
+        <v>46131.30746527778</v>
       </c>
       <c r="E50">
         <v>30680</v>
@@ -9599,7 +9599,7 @@
         <v>46131.3078321875</v>
       </c>
       <c r="D51" s="1">
-        <v>46131.5578125</v>
+        <v>46131.3078125</v>
       </c>
       <c r="E51">
         <v>31307</v>
@@ -9742,7 +9742,7 @@
         <v>46131.30817962963</v>
       </c>
       <c r="D52" s="1">
-        <v>46131.55815972222</v>
+        <v>46131.30815972222</v>
       </c>
       <c r="E52">
         <v>31959</v>
@@ -9885,7 +9885,7 @@
         <v>46131.30852662037</v>
       </c>
       <c r="D53" s="1">
-        <v>46131.55850694444</v>
+        <v>46131.30850694444</v>
       </c>
       <c r="E53">
         <v>32485</v>
@@ -10028,7 +10028,7 @@
         <v>46131.30887375</v>
       </c>
       <c r="D54" s="1">
-        <v>46131.558854166666</v>
+        <v>46131.308854166666</v>
       </c>
       <c r="E54">
         <v>33204</v>
@@ -10171,7 +10171,7 @@
         <v>46131.309221689815</v>
       </c>
       <c r="D55" s="1">
-        <v>46131.55920138889</v>
+        <v>46131.30920138889</v>
       </c>
       <c r="E55">
         <v>33885</v>
@@ -10314,7 +10314,7 @@
         <v>46131.30956865741</v>
       </c>
       <c r="D56" s="1">
-        <v>46131.55954861111</v>
+        <v>46131.30954861111</v>
       </c>
       <c r="E56">
         <v>34533</v>
@@ -10457,7 +10457,7 @@
         <v>46131.30991578704</v>
       </c>
       <c r="D57" s="1">
-        <v>46131.559895833336</v>
+        <v>46131.309895833336</v>
       </c>
       <c r="E57">
         <v>35187</v>
@@ -10600,7 +10600,7 @@
         <v>46131.31026287037</v>
       </c>
       <c r="D58" s="1">
-        <v>46131.56024305556</v>
+        <v>46131.31024305556</v>
       </c>
       <c r="E58">
         <v>35911</v>
@@ -10743,7 +10743,7 @@
         <v>46131.31061008102</v>
       </c>
       <c r="D59" s="1">
-        <v>46131.560590277775</v>
+        <v>46131.310590277775</v>
       </c>
       <c r="E59">
         <v>36645</v>
@@ -10886,7 +10886,7 @@
         <v>46131.31096446759</v>
       </c>
       <c r="D60" s="1">
-        <v>46131.5609375</v>
+        <v>46131.3109375</v>
       </c>
       <c r="E60">
         <v>37233</v>
@@ -11032,7 +11032,7 @@
         <v>46131.31130454861</v>
       </c>
       <c r="D61" s="1">
-        <v>46131.56128472222</v>
+        <v>46131.31128472222</v>
       </c>
       <c r="E61">
         <v>37537</v>
@@ -11175,7 +11175,7 @@
         <v>46131.31165171296</v>
       </c>
       <c r="D62" s="1">
-        <v>46131.561631944445</v>
+        <v>46131.311631944445</v>
       </c>
       <c r="E62">
         <v>37827</v>
@@ -11318,7 +11318,7 @@
         <v>46131.31199888889</v>
       </c>
       <c r="D63" s="1">
-        <v>46131.56197916667</v>
+        <v>46131.31197916667</v>
       </c>
       <c r="E63">
         <v>38421</v>
@@ -11461,7 +11461,7 @@
         <v>46131.31234643519</v>
       </c>
       <c r="D64" s="1">
-        <v>46131.56232638889</v>
+        <v>46131.31232638889</v>
       </c>
       <c r="E64">
         <v>38782</v>
@@ -11604,7 +11604,7 @@
         <v>46131.31269372685</v>
       </c>
       <c r="D65" s="1">
-        <v>46131.56267361111</v>
+        <v>46131.31267361111</v>
       </c>
       <c r="E65">
         <v>39183</v>
@@ -11747,7 +11747,7 @@
         <v>46131.313049351855</v>
       </c>
       <c r="D66" s="1">
-        <v>46131.56302083333</v>
+        <v>46131.31302083333</v>
       </c>
       <c r="E66">
         <v>39562</v>
@@ -11890,7 +11890,7 @@
         <v>46131.31338774306</v>
       </c>
       <c r="D67" s="1">
-        <v>46131.563368055555</v>
+        <v>46131.313368055555</v>
       </c>
       <c r="E67">
         <v>39907</v>
@@ -12033,7 +12033,7 @@
         <v>46131.31373505787</v>
       </c>
       <c r="D68" s="1">
-        <v>46131.56371527778</v>
+        <v>46131.31371527778</v>
       </c>
       <c r="E68">
         <v>40242</v>
@@ -12176,7 +12176,7 @@
         <v>46131.31404982639</v>
       </c>
       <c r="D69" s="1">
-        <v>46131.563993055555</v>
+        <v>46131.313993055555</v>
       </c>
       <c r="E69">
         <v>40458</v>
@@ -12319,7 +12319,7 @@
         <v>46131.31408241898</v>
       </c>
       <c r="D70" s="1">
-        <v>46131.5640625</v>
+        <v>46131.3140625</v>
       </c>
       <c r="E70">
         <v>40622</v>
@@ -12462,7 +12462,7 @@
         <v>46131.314429398146</v>
       </c>
       <c r="D71" s="1">
-        <v>46131.564409722225</v>
+        <v>46131.314409722225</v>
       </c>
       <c r="E71">
         <v>41193</v>
@@ -12605,7 +12605,7 @@
         <v>46131.3147765625</v>
       </c>
       <c r="D72" s="1">
-        <v>46131.56475694444</v>
+        <v>46131.31475694444</v>
       </c>
       <c r="E72">
         <v>41665</v>
@@ -12748,7 +12748,7 @@
         <v>46131.315123506945</v>
       </c>
       <c r="D73" s="1">
-        <v>46131.565104166664</v>
+        <v>46131.315104166664</v>
       </c>
       <c r="E73">
         <v>41968</v>
@@ -12891,7 +12891,7 @@
         <v>46131.31547109954</v>
       </c>
       <c r="D74" s="1">
-        <v>46131.56545138889</v>
+        <v>46131.31545138889</v>
       </c>
       <c r="E74">
         <v>42279</v>
@@ -13034,7 +13034,7 @@
         <v>46131.31581799768</v>
       </c>
       <c r="D75" s="1">
-        <v>46131.56579861111</v>
+        <v>46131.31579861111</v>
       </c>
       <c r="E75">
         <v>42670</v>
@@ -13177,7 +13177,7 @@
         <v>46131.31617633102</v>
       </c>
       <c r="D76" s="1">
-        <v>46131.566145833334</v>
+        <v>46131.316145833334</v>
       </c>
       <c r="E76">
         <v>43033</v>
@@ -13320,7 +13320,7 @@
         <v>46131.316523587964</v>
       </c>
       <c r="D77" s="1">
-        <v>46131.56649305556</v>
+        <v>46131.31649305556</v>
       </c>
       <c r="E77">
         <v>43340</v>
@@ -13463,7 +13463,7 @@
         <v>46131.31687603009</v>
       </c>
       <c r="D78" s="1">
-        <v>46131.56684027778</v>
+        <v>46131.31684027778</v>
       </c>
       <c r="E78">
         <v>43674</v>
@@ -13606,7 +13606,7 @@
         <v>46131.317207534725</v>
       </c>
       <c r="D79" s="1">
-        <v>46131.5671875</v>
+        <v>46131.3171875</v>
       </c>
       <c r="E79">
         <v>44032</v>
@@ -13749,7 +13749,7 @@
         <v>46131.31755423611</v>
       </c>
       <c r="D80" s="1">
-        <v>46131.56753472222</v>
+        <v>46131.31753472222</v>
       </c>
       <c r="E80">
         <v>44418</v>
@@ -13892,7 +13892,7 @@
         <v>46131.31790190972</v>
       </c>
       <c r="D81" s="1">
-        <v>46131.567881944444</v>
+        <v>46131.317881944444</v>
       </c>
       <c r="E81">
         <v>44773</v>
@@ -14035,7 +14035,7 @@
         <v>46131.31824898148</v>
       </c>
       <c r="D82" s="1">
-        <v>46131.56822916667</v>
+        <v>46131.31822916667</v>
       </c>
       <c r="E82">
         <v>45109</v>
@@ -14178,7 +14178,7 @@
         <v>46131.31859585648</v>
       </c>
       <c r="D83" s="1">
-        <v>46131.56857638889</v>
+        <v>46131.31857638889</v>
       </c>
       <c r="E83">
         <v>45449</v>
@@ -14321,7 +14321,7 @@
         <v>46131.318943252314</v>
       </c>
       <c r="D84" s="1">
-        <v>46131.568923611114</v>
+        <v>46131.318923611114</v>
       </c>
       <c r="E84">
         <v>45744</v>
@@ -14464,7 +14464,7 @@
         <v>46131.31929048611</v>
       </c>
       <c r="D85" s="1">
-        <v>46131.56927083333</v>
+        <v>46131.31927083333</v>
       </c>
       <c r="E85">
         <v>46066</v>
@@ -14607,7 +14607,7 @@
         <v>46131.31963759259</v>
       </c>
       <c r="D86" s="1">
-        <v>46131.56961805555</v>
+        <v>46131.31961805555</v>
       </c>
       <c r="E86">
         <v>46383</v>
@@ -14750,7 +14750,7 @@
         <v>46131.31998782408</v>
       </c>
       <c r="D87" s="1">
-        <v>46131.56996527778</v>
+        <v>46131.31996527778</v>
       </c>
       <c r="E87">
         <v>46821</v>
@@ -14893,7 +14893,7 @@
         <v>46131.32033418981</v>
       </c>
       <c r="D88" s="1">
-        <v>46131.5703125</v>
+        <v>46131.3203125</v>
       </c>
       <c r="E88">
         <v>47198</v>
@@ -15036,7 +15036,7 @@
         <v>46131.32067951389</v>
       </c>
       <c r="D89" s="1">
-        <v>46131.57065972222</v>
+        <v>46131.32065972222</v>
       </c>
       <c r="E89">
         <v>47576</v>
@@ -15179,7 +15179,7 @@
         <v>46131.32102688657</v>
       </c>
       <c r="D90" s="1">
-        <v>46131.57100694445</v>
+        <v>46131.32100694445</v>
       </c>
       <c r="E90">
         <v>47964</v>
@@ -15322,7 +15322,7 @@
         <v>46131.32137666667</v>
       </c>
       <c r="D91" s="1">
-        <v>46131.57135416667</v>
+        <v>46131.32135416667</v>
       </c>
       <c r="E91">
         <v>48365</v>
@@ -15465,7 +15465,7 @@
         <v>46131.321721134256</v>
       </c>
       <c r="D92" s="1">
-        <v>46131.571701388886</v>
+        <v>46131.321701388886</v>
       </c>
       <c r="E92">
         <v>48775</v>
@@ -15608,7 +15608,7 @@
         <v>46131.32206770833</v>
       </c>
       <c r="D93" s="1">
-        <v>46131.57204861111</v>
+        <v>46131.32204861111</v>
       </c>
       <c r="E93">
         <v>49124</v>
@@ -15751,7 +15751,7 @@
         <v>46131.3224178125</v>
       </c>
       <c r="D94" s="1">
-        <v>46131.57239583333</v>
+        <v>46131.32239583333</v>
       </c>
       <c r="E94">
         <v>49443</v>
@@ -15894,7 +15894,7 @@
         <v>46131.322762268515</v>
       </c>
       <c r="D95" s="1">
-        <v>46131.572743055556</v>
+        <v>46131.322743055556</v>
       </c>
       <c r="E95">
         <v>49744</v>
@@ -16037,7 +16037,7 @@
         <v>46131.32310971065</v>
       </c>
       <c r="D96" s="1">
-        <v>46131.57309027778</v>
+        <v>46131.32309027778</v>
       </c>
       <c r="E96">
         <v>50047</v>
@@ -16180,7 +16180,7 @@
         <v>46131.32345658565</v>
       </c>
       <c r="D97" s="1">
-        <v>46131.5734375</v>
+        <v>46131.3234375</v>
       </c>
       <c r="E97">
         <v>50427</v>
@@ -16323,7 +16323,7 @@
         <v>46131.32380449074</v>
       </c>
       <c r="D98" s="1">
-        <v>46131.57378472222</v>
+        <v>46131.32378472222</v>
       </c>
       <c r="E98">
         <v>50834</v>
@@ -16466,7 +16466,7 @@
         <v>46131.32415144676</v>
       </c>
       <c r="D99" s="1">
-        <v>46131.57413194444</v>
+        <v>46131.32413194444</v>
       </c>
       <c r="E99">
         <v>51233</v>
@@ -16609,7 +16609,7 @@
         <v>46131.32449835648</v>
       </c>
       <c r="D100" s="1">
-        <v>46131.574479166666</v>
+        <v>46131.324479166666</v>
       </c>
       <c r="E100">
         <v>51682</v>
@@ -16752,7 +16752,7 @@
         <v>46131.32484570602</v>
       </c>
       <c r="D101" s="1">
-        <v>46131.57482638889</v>
+        <v>46131.32482638889</v>
       </c>
       <c r="E101">
         <v>52149</v>
@@ -16895,7 +16895,7 @@
         <v>46131.32519369213</v>
       </c>
       <c r="D102" s="1">
-        <v>46131.57517361111</v>
+        <v>46131.32517361111</v>
       </c>
       <c r="E102">
         <v>52642</v>
@@ -17038,7 +17038,7 @@
         <v>46131.32553997685</v>
       </c>
       <c r="D103" s="1">
-        <v>46131.575520833336</v>
+        <v>46131.325520833336</v>
       </c>
       <c r="E103">
         <v>53089</v>
@@ -17181,7 +17181,7 @@
         <v>46131.32588795139</v>
       </c>
       <c r="D104" s="1">
-        <v>46131.57586805556</v>
+        <v>46131.32586805556</v>
       </c>
       <c r="E104">
         <v>53496</v>
@@ -17324,7 +17324,7 @@
         <v>46131.326234849534</v>
       </c>
       <c r="D105" s="1">
-        <v>46131.576215277775</v>
+        <v>46131.326215277775</v>
       </c>
       <c r="E105">
         <v>53862</v>
@@ -17467,7 +17467,7 @@
         <v>46131.32658230324</v>
       </c>
       <c r="D106" s="1">
-        <v>46131.5765625</v>
+        <v>46131.3265625</v>
       </c>
       <c r="E106">
         <v>54185</v>
@@ -17610,7 +17610,7 @@
         <v>46131.32693142361</v>
       </c>
       <c r="D107" s="1">
-        <v>46131.57690972222</v>
+        <v>46131.32690972222</v>
       </c>
       <c r="E107">
         <v>54472</v>
@@ -17753,7 +17753,7 @@
         <v>46131.3272765625</v>
       </c>
       <c r="D108" s="1">
-        <v>46131.577256944445</v>
+        <v>46131.327256944445</v>
       </c>
       <c r="E108">
         <v>54792</v>
@@ -17896,7 +17896,7 @@
         <v>46131.32762532408</v>
       </c>
       <c r="D109" s="1">
-        <v>46131.57760416667</v>
+        <v>46131.32760416667</v>
       </c>
       <c r="E109">
         <v>55239</v>
@@ -18039,7 +18039,7 @@
         <v>46131.32797076389</v>
       </c>
       <c r="D110" s="1">
-        <v>46131.57795138889</v>
+        <v>46131.32795138889</v>
       </c>
       <c r="E110">
         <v>55619</v>
@@ -18182,7 +18182,7 @@
         <v>46131.32831780092</v>
       </c>
       <c r="D111" s="1">
-        <v>46131.57829861111</v>
+        <v>46131.32829861111</v>
       </c>
       <c r="E111">
         <v>56120</v>
@@ -18325,7 +18325,7 @@
         <v>46131.32866535879</v>
       </c>
       <c r="D112" s="1">
-        <v>46131.57864583333</v>
+        <v>46131.32864583333</v>
       </c>
       <c r="E112">
         <v>56630</v>
@@ -18468,7 +18468,7 @@
         <v>46131.32901530093</v>
       </c>
       <c r="D113" s="1">
-        <v>46131.578993055555</v>
+        <v>46131.328993055555</v>
       </c>
       <c r="E113">
         <v>57100</v>
@@ -18611,7 +18611,7 @@
         <v>46131.32935989583</v>
       </c>
       <c r="D114" s="1">
-        <v>46131.57934027778</v>
+        <v>46131.32934027778</v>
       </c>
       <c r="E114">
         <v>57671</v>
@@ -18754,7 +18754,7 @@
         <v>46131.32970707176</v>
       </c>
       <c r="D115" s="1">
-        <v>46131.5796875</v>
+        <v>46131.3296875</v>
       </c>
       <c r="E115">
         <v>58024</v>
@@ -18897,7 +18897,7 @@
         <v>46131.33005399306</v>
       </c>
       <c r="D116" s="1">
-        <v>46131.580034722225</v>
+        <v>46131.330034722225</v>
       </c>
       <c r="E116">
         <v>58351</v>
@@ -19040,7 +19040,7 @@
         <v>46131.33040429398</v>
       </c>
       <c r="D117" s="1">
-        <v>46131.58038194444</v>
+        <v>46131.33038194444</v>
       </c>
       <c r="E117">
         <v>58641</v>
@@ -19183,7 +19183,7 @@
         <v>46131.33075054398</v>
       </c>
       <c r="D118" s="1">
-        <v>46131.580729166664</v>
+        <v>46131.330729166664</v>
       </c>
       <c r="E118">
         <v>58907</v>
@@ -19326,7 +19326,7 @@
         <v>46131.33109738426</v>
       </c>
       <c r="D119" s="1">
-        <v>46131.58107638889</v>
+        <v>46131.33107638889</v>
       </c>
       <c r="E119">
         <v>59221</v>
@@ -19469,7 +19469,7 @@
         <v>46131.33144328704</v>
       </c>
       <c r="D120" s="1">
-        <v>46131.58142361111</v>
+        <v>46131.33142361111</v>
       </c>
       <c r="E120">
         <v>59602</v>
@@ -19612,7 +19612,7 @@
         <v>46131.3317925463</v>
       </c>
       <c r="D121" s="1">
-        <v>46131.581770833334</v>
+        <v>46131.331770833334</v>
       </c>
       <c r="E121">
         <v>60008</v>
@@ -19755,7 +19755,7 @@
         <v>46131.3321380787</v>
       </c>
       <c r="D122" s="1">
-        <v>46131.58211805556</v>
+        <v>46131.33211805556</v>
       </c>
       <c r="E122">
         <v>60503</v>
@@ -19898,7 +19898,7 @@
         <v>46131.332486631945</v>
       </c>
       <c r="D123" s="1">
-        <v>46131.58246527778</v>
+        <v>46131.33246527778</v>
       </c>
       <c r="E123">
         <v>60945</v>
@@ -20041,7 +20041,7 @@
         <v>46131.33283412037</v>
       </c>
       <c r="D124" s="1">
-        <v>46131.5828125</v>
+        <v>46131.3328125</v>
       </c>
       <c r="E124">
         <v>61323</v>
@@ -20184,7 +20184,7 @@
         <v>46131.33318179398</v>
       </c>
       <c r="D125" s="1">
-        <v>46131.58315972222</v>
+        <v>46131.33315972222</v>
       </c>
       <c r="E125">
         <v>61745</v>
@@ -20327,7 +20327,7 @@
         <v>46131.33352854167</v>
       </c>
       <c r="D126" s="1">
-        <v>46131.583506944444</v>
+        <v>46131.333506944444</v>
       </c>
       <c r="E126">
         <v>62359</v>
@@ -20470,7 +20470,7 @@
         <v>46131.33387560185</v>
       </c>
       <c r="D127" s="1">
-        <v>46131.58385416667</v>
+        <v>46131.33385416667</v>
       </c>
       <c r="E127">
         <v>62778</v>
@@ -20613,7 +20613,7 @@
         <v>46131.334220972225</v>
       </c>
       <c r="D128" s="1">
-        <v>46131.58420138889</v>
+        <v>46131.33420138889</v>
       </c>
       <c r="E128">
         <v>63249</v>
@@ -20756,7 +20756,7 @@
         <v>46131.33456846065</v>
       </c>
       <c r="D129" s="1">
-        <v>46131.584548611114</v>
+        <v>46131.334548611114</v>
       </c>
       <c r="E129">
         <v>63753</v>
@@ -20899,7 +20899,7 @@
         <v>46131.33491563657</v>
       </c>
       <c r="D130" s="1">
-        <v>46131.58489583333</v>
+        <v>46131.33489583333</v>
       </c>
       <c r="E130">
         <v>64335</v>
@@ -21042,7 +21042,7 @@
         <v>46131.33526425926</v>
       </c>
       <c r="D131" s="1">
-        <v>46131.58524305555</v>
+        <v>46131.33524305555</v>
       </c>
       <c r="E131">
         <v>64885</v>
@@ -21185,7 +21185,7 @@
         <v>46131.33561181713</v>
       </c>
       <c r="D132" s="1">
-        <v>46131.58559027778</v>
+        <v>46131.33559027778</v>
       </c>
       <c r="E132">
         <v>65360</v>
@@ -21328,7 +21328,7 @@
         <v>46131.33595956019</v>
       </c>
       <c r="D133" s="1">
-        <v>46131.5859375</v>
+        <v>46131.3359375</v>
       </c>
       <c r="E133">
         <v>65885</v>
@@ -21471,7 +21471,7 @@
         <v>46131.3363040625</v>
       </c>
       <c r="D134" s="1">
-        <v>46131.58628472222</v>
+        <v>46131.33628472222</v>
       </c>
       <c r="E134">
         <v>66329</v>
@@ -21614,7 +21614,7 @@
         <v>46131.33666759259</v>
       </c>
       <c r="D135" s="1">
-        <v>46131.58663194445</v>
+        <v>46131.33663194445</v>
       </c>
       <c r="E135">
         <v>66687</v>
@@ -21757,7 +21757,7 @@
         <v>46131.33699891204</v>
       </c>
       <c r="D136" s="1">
-        <v>46131.58697916667</v>
+        <v>46131.33697916667</v>
       </c>
       <c r="E136">
         <v>67046</v>
@@ -21900,7 +21900,7 @@
         <v>46131.3373484375</v>
       </c>
       <c r="D137" s="1">
-        <v>46131.587326388886</v>
+        <v>46131.337326388886</v>
       </c>
       <c r="E137">
         <v>67437</v>
@@ -22043,7 +22043,7 @@
         <v>46131.3376933912</v>
       </c>
       <c r="D138" s="1">
-        <v>46131.58767361111</v>
+        <v>46131.33767361111</v>
       </c>
       <c r="E138">
         <v>67847</v>
@@ -22186,7 +22186,7 @@
         <v>46131.338041944444</v>
       </c>
       <c r="D139" s="1">
-        <v>46131.58802083333</v>
+        <v>46131.33802083333</v>
       </c>
       <c r="E139">
         <v>68350</v>
@@ -22329,7 +22329,7 @@
         <v>46131.33838787037</v>
       </c>
       <c r="D140" s="1">
-        <v>46131.588368055556</v>
+        <v>46131.338368055556</v>
       </c>
       <c r="E140">
         <v>68856</v>
@@ -22472,7 +22472,7 @@
         <v>46131.338734895835</v>
       </c>
       <c r="D141" s="1">
-        <v>46131.58871527778</v>
+        <v>46131.33871527778</v>
       </c>
       <c r="E141">
         <v>69404</v>
@@ -22615,7 +22615,7 @@
         <v>46131.33908189815</v>
       </c>
       <c r="D142" s="1">
-        <v>46131.5890625</v>
+        <v>46131.3390625</v>
       </c>
       <c r="E142">
         <v>69888</v>
@@ -22758,7 +22758,7 @@
         <v>46131.33942912037</v>
       </c>
       <c r="D143" s="1">
-        <v>46131.58940972222</v>
+        <v>46131.33940972222</v>
       </c>
       <c r="E143">
         <v>70335</v>
@@ -22901,7 +22901,7 @@
         <v>46131.339776354165</v>
       </c>
       <c r="D144" s="1">
-        <v>46131.58975694444</v>
+        <v>46131.33975694444</v>
       </c>
       <c r="E144">
         <v>70748</v>
@@ -23044,7 +23044,7 @@
         <v>46131.34012599537</v>
       </c>
       <c r="D145" s="1">
-        <v>46131.590104166666</v>
+        <v>46131.340104166666</v>
       </c>
       <c r="E145">
         <v>71202</v>
@@ -23187,7 +23187,7 @@
         <v>46131.3404728125</v>
       </c>
       <c r="D146" s="1">
-        <v>46131.59045138889</v>
+        <v>46131.34045138889</v>
       </c>
       <c r="E146">
         <v>71663</v>
@@ -23330,7 +23330,7 @@
         <v>46131.340818020835</v>
       </c>
       <c r="D147" s="1">
-        <v>46131.59079861111</v>
+        <v>46131.34079861111</v>
       </c>
       <c r="E147">
         <v>72031</v>
@@ -23473,7 +23473,7 @@
         <v>46131.34116560185</v>
       </c>
       <c r="D148" s="1">
-        <v>46131.591145833336</v>
+        <v>46131.341145833336</v>
       </c>
       <c r="E148">
         <v>72404</v>
@@ -23616,7 +23616,7 @@
         <v>46131.34151521991</v>
       </c>
       <c r="D149" s="1">
-        <v>46131.59149305556</v>
+        <v>46131.34149305556</v>
       </c>
       <c r="E149">
         <v>72819</v>
@@ -23759,7 +23759,7 @@
         <v>46131.3418596412</v>
       </c>
       <c r="D150" s="1">
-        <v>46131.591840277775</v>
+        <v>46131.341840277775</v>
       </c>
       <c r="E150">
         <v>73277</v>
@@ -23902,7 +23902,7 @@
         <v>46131.342207291666</v>
       </c>
       <c r="D151" s="1">
-        <v>46131.5921875</v>
+        <v>46131.3421875</v>
       </c>
       <c r="E151">
         <v>73810</v>
@@ -24045,7 +24045,7 @@
         <v>46131.34255461806</v>
       </c>
       <c r="D152" s="1">
-        <v>46131.59253472222</v>
+        <v>46131.34253472222</v>
       </c>
       <c r="E152">
         <v>74358</v>
@@ -24188,7 +24188,7 @@
         <v>46131.342910416664</v>
       </c>
       <c r="D153" s="1">
-        <v>46131.592881944445</v>
+        <v>46131.342881944445</v>
       </c>
       <c r="E153">
         <v>74881</v>
@@ -24331,7 +24331,7 @@
         <v>46131.34324960648</v>
       </c>
       <c r="D154" s="1">
-        <v>46131.59322916667</v>
+        <v>46131.34322916667</v>
       </c>
       <c r="E154">
         <v>75426</v>
@@ -24474,7 +24474,7 @@
         <v>46131.34359928241</v>
       </c>
       <c r="D155" s="1">
-        <v>46131.59357638889</v>
+        <v>46131.34357638889</v>
       </c>
       <c r="E155">
         <v>76026</v>
@@ -24617,7 +24617,7 @@
         <v>46131.34394361111</v>
       </c>
       <c r="D156" s="1">
-        <v>46131.59392361111</v>
+        <v>46131.34392361111</v>
       </c>
       <c r="E156">
         <v>76462</v>
@@ -24760,7 +24760,7 @@
         <v>46131.34429069445</v>
       </c>
       <c r="D157" s="1">
-        <v>46131.59427083333</v>
+        <v>46131.34427083333</v>
       </c>
       <c r="E157">
         <v>76902</v>
@@ -24903,7 +24903,7 @@
         <v>46131.344638159724</v>
       </c>
       <c r="D158" s="1">
-        <v>46131.594618055555</v>
+        <v>46131.344618055555</v>
       </c>
       <c r="E158">
         <v>77365</v>
@@ -25046,7 +25046,7 @@
         <v>46131.34498505787</v>
       </c>
       <c r="D159" s="1">
-        <v>46131.59496527778</v>
+        <v>46131.34496527778</v>
       </c>
       <c r="E159">
         <v>77857</v>
@@ -25189,7 +25189,7 @@
         <v>46131.34533196759</v>
       </c>
       <c r="D160" s="1">
-        <v>46131.5953125</v>
+        <v>46131.3453125</v>
       </c>
       <c r="E160">
         <v>78361</v>
@@ -25332,7 +25332,7 @@
         <v>46131.34568212963</v>
       </c>
       <c r="D161" s="1">
-        <v>46131.595659722225</v>
+        <v>46131.345659722225</v>
       </c>
       <c r="E161">
         <v>78970</v>
@@ -25475,7 +25475,7 @@
         <v>46131.34602642361</v>
       </c>
       <c r="D162" s="1">
-        <v>46131.59600694444</v>
+        <v>46131.34600694444</v>
       </c>
       <c r="E162">
         <v>79531</v>
@@ -25618,7 +25618,7 @@
         <v>46131.3463765162</v>
       </c>
       <c r="D163" s="1">
-        <v>46131.596354166664</v>
+        <v>46131.346354166664</v>
       </c>
       <c r="E163">
         <v>80011</v>
@@ -25761,7 +25761,7 @@
         <v>46131.34672084491</v>
       </c>
       <c r="D164" s="1">
-        <v>46131.59670138889</v>
+        <v>46131.34670138889</v>
       </c>
       <c r="E164">
         <v>80412</v>
@@ -25904,7 +25904,7 @@
         <v>46131.34706835648</v>
       </c>
       <c r="D165" s="1">
-        <v>46131.59704861111</v>
+        <v>46131.34704861111</v>
       </c>
       <c r="E165">
         <v>80782</v>
@@ -26047,7 +26047,7 @@
         <v>46131.34741855324</v>
       </c>
       <c r="D166" s="1">
-        <v>46131.597395833334</v>
+        <v>46131.347395833334</v>
       </c>
       <c r="E166">
         <v>81151</v>
@@ -26190,7 +26190,7 @@
         <v>46131.34776292824</v>
       </c>
       <c r="D167" s="1">
-        <v>46131.59774305556</v>
+        <v>46131.34774305556</v>
       </c>
       <c r="E167">
         <v>81544</v>
@@ -26333,7 +26333,7 @@
         <v>46131.34811009259</v>
       </c>
       <c r="D168" s="1">
-        <v>46131.59809027778</v>
+        <v>46131.34809027778</v>
       </c>
       <c r="E168">
         <v>81934</v>
@@ -26476,7 +26476,7 @@
         <v>46131.348460810186</v>
       </c>
       <c r="D169" s="1">
-        <v>46131.5984375</v>
+        <v>46131.3484375</v>
       </c>
       <c r="E169">
         <v>82358</v>
@@ -26619,7 +26619,7 @@
         <v>46131.34880381944</v>
       </c>
       <c r="D170" s="1">
-        <v>46131.59878472222</v>
+        <v>46131.34878472222</v>
       </c>
       <c r="E170">
         <v>82833</v>
@@ -26762,7 +26762,7 @@
         <v>46131.349151469905</v>
       </c>
       <c r="D171" s="1">
-        <v>46131.599131944444</v>
+        <v>46131.349131944444</v>
       </c>
       <c r="E171">
         <v>83316</v>
@@ -26905,7 +26905,7 @@
         <v>46131.34949869213</v>
       </c>
       <c r="D172" s="1">
-        <v>46131.59947916667</v>
+        <v>46131.34947916667</v>
       </c>
       <c r="E172">
         <v>83849</v>
@@ -27204,7 +27204,7 @@
         <v>46131.34984630787</v>
       </c>
       <c r="D2" s="1">
-        <v>46131.59982638889</v>
+        <v>46131.34982638889</v>
       </c>
       <c r="E2">
         <v>82404</v>
@@ -27311,7 +27311,7 @@
         <v>46131.35019336805</v>
       </c>
       <c r="D3" s="1">
-        <v>46131.600173611114</v>
+        <v>46131.350173611114</v>
       </c>
       <c r="E3">
         <v>79506</v>
@@ -27442,7 +27442,7 @@
         <v>46131.35054291667</v>
       </c>
       <c r="D4" s="1">
-        <v>46131.60052083333</v>
+        <v>46131.35052083333</v>
       </c>
       <c r="E4">
         <v>76819</v>
@@ -27585,7 +27585,7 @@
         <v>46131.35088702547</v>
       </c>
       <c r="D5" s="1">
-        <v>46131.60086805555</v>
+        <v>46131.35086805555</v>
       </c>
       <c r="E5">
         <v>74153</v>
@@ -27728,7 +27728,7 @@
         <v>46131.35123545139</v>
       </c>
       <c r="D6" s="1">
-        <v>46131.60121527778</v>
+        <v>46131.35121527778</v>
       </c>
       <c r="E6">
         <v>71738</v>
@@ -27871,7 +27871,7 @@
         <v>46131.351582731484</v>
       </c>
       <c r="D7" s="1">
-        <v>46131.6015625</v>
+        <v>46131.3515625</v>
       </c>
       <c r="E7">
         <v>69539</v>
@@ -28014,7 +28014,7 @@
         <v>46131.35192929398</v>
       </c>
       <c r="D8" s="1">
-        <v>46131.60190972222</v>
+        <v>46131.35190972222</v>
       </c>
       <c r="E8">
         <v>67384</v>
@@ -28157,7 +28157,7 @@
         <v>46131.3522771412</v>
       </c>
       <c r="D9" s="1">
-        <v>46131.60225694445</v>
+        <v>46131.35225694445</v>
       </c>
       <c r="E9">
         <v>65370</v>
@@ -28300,7 +28300,7 @@
         <v>46131.35262373843</v>
       </c>
       <c r="D10" s="1">
-        <v>46131.60260416667</v>
+        <v>46131.35260416667</v>
       </c>
       <c r="E10">
         <v>63629</v>
@@ -28443,7 +28443,7 @@
         <v>46131.352974421294</v>
       </c>
       <c r="D11" s="1">
-        <v>46131.602951388886</v>
+        <v>46131.352951388886</v>
       </c>
       <c r="E11">
         <v>61975</v>
@@ -28586,7 +28586,7 @@
         <v>46131.35331806713</v>
       </c>
       <c r="D12" s="1">
-        <v>46131.60329861111</v>
+        <v>46131.35329861111</v>
       </c>
       <c r="E12">
         <v>60424</v>
@@ -28729,7 +28729,7 @@
         <v>46131.35366810185</v>
       </c>
       <c r="D13" s="1">
-        <v>46131.60364583333</v>
+        <v>46131.35364583333</v>
       </c>
       <c r="E13">
         <v>58943</v>
@@ -28872,7 +28872,7 @@
         <v>46131.35402982639</v>
       </c>
       <c r="D14" s="1">
-        <v>46131.603993055556</v>
+        <v>46131.353993055556</v>
       </c>
       <c r="E14">
         <v>57436</v>
@@ -29015,7 +29015,7 @@
         <v>46131.35435976852</v>
       </c>
       <c r="D15" s="1">
-        <v>46131.60434027778</v>
+        <v>46131.35434027778</v>
       </c>
       <c r="E15">
         <v>55849</v>
@@ -29158,7 +29158,7 @@
         <v>46131.3547100463</v>
       </c>
       <c r="D16" s="1">
-        <v>46131.6046875</v>
+        <v>46131.3546875</v>
       </c>
       <c r="E16">
         <v>54320</v>
@@ -29301,7 +29301,7 @@
         <v>46131.355054594904</v>
       </c>
       <c r="D17" s="1">
-        <v>46131.60503472222</v>
+        <v>46131.35503472222</v>
       </c>
       <c r="E17">
         <v>52837</v>
@@ -29444,7 +29444,7 @@
         <v>46131.35540528935</v>
       </c>
       <c r="D18" s="1">
-        <v>46131.60538194444</v>
+        <v>46131.35538194444</v>
       </c>
       <c r="E18">
         <v>51361</v>
@@ -29587,7 +29587,7 @@
         <v>46131.35574931713</v>
       </c>
       <c r="D19" s="1">
-        <v>46131.605729166666</v>
+        <v>46131.355729166666</v>
       </c>
       <c r="E19">
         <v>50117</v>
@@ -29730,7 +29730,7 @@
         <v>46131.35609649306</v>
       </c>
       <c r="D20" s="1">
-        <v>46131.60607638889</v>
+        <v>46131.35607638889</v>
       </c>
       <c r="E20">
         <v>48969</v>
@@ -29873,7 +29873,7 @@
         <v>46131.35644326389</v>
       </c>
       <c r="D21" s="1">
-        <v>46131.60642361111</v>
+        <v>46131.35642361111</v>
       </c>
       <c r="E21">
         <v>47835</v>
@@ -30016,7 +30016,7 @@
         <v>46131.3567927662</v>
       </c>
       <c r="D22" s="1">
-        <v>46131.606770833336</v>
+        <v>46131.356770833336</v>
       </c>
       <c r="E22">
         <v>46684</v>
@@ -30159,7 +30159,7 @@
         <v>46131.35713737269</v>
       </c>
       <c r="D23" s="1">
-        <v>46131.60711805556</v>
+        <v>46131.35711805556</v>
       </c>
       <c r="E23">
         <v>45575</v>
@@ -30302,7 +30302,7 @@
         <v>46131.357484988424</v>
       </c>
       <c r="D24" s="1">
-        <v>46131.607465277775</v>
+        <v>46131.357465277775</v>
       </c>
       <c r="E24">
         <v>44497</v>
@@ -30445,7 +30445,7 @@
         <v>46131.35783248843</v>
       </c>
       <c r="D25" s="1">
-        <v>46131.6078125</v>
+        <v>46131.3578125</v>
       </c>
       <c r="E25">
         <v>43455</v>
@@ -30588,7 +30588,7 @@
         <v>46131.358182488424</v>
       </c>
       <c r="D26" s="1">
-        <v>46131.60815972222</v>
+        <v>46131.35815972222</v>
       </c>
       <c r="E26">
         <v>42435</v>
@@ -30731,7 +30731,7 @@
         <v>46131.35852670139</v>
       </c>
       <c r="D27" s="1">
-        <v>46131.608506944445</v>
+        <v>46131.358506944445</v>
       </c>
       <c r="E27">
         <v>41449</v>
@@ -30874,7 +30874,7 @@
         <v>46131.3588740625</v>
       </c>
       <c r="D28" s="1">
-        <v>46131.60885416667</v>
+        <v>46131.35885416667</v>
       </c>
       <c r="E28">
         <v>40487</v>
@@ -31017,7 +31017,7 @@
         <v>46131.3592209375</v>
       </c>
       <c r="D29" s="1">
-        <v>46131.60920138889</v>
+        <v>46131.35920138889</v>
       </c>
       <c r="E29">
         <v>39544</v>
@@ -31160,7 +31160,7 @@
         <v>46131.359569328706</v>
       </c>
       <c r="D30" s="1">
-        <v>46131.60954861111</v>
+        <v>46131.35954861111</v>
       </c>
       <c r="E30">
         <v>38643</v>
@@ -31303,7 +31303,7 @@
         <v>46131.359915740744</v>
       </c>
       <c r="D31" s="1">
-        <v>46131.60989583333</v>
+        <v>46131.35989583333</v>
       </c>
       <c r="E31">
         <v>37748</v>
@@ -31446,7 +31446,7 @@
         <v>46131.36026584491</v>
       </c>
       <c r="D32" s="1">
-        <v>46131.610243055555</v>
+        <v>46131.360243055555</v>
       </c>
       <c r="E32">
         <v>36847</v>
@@ -31589,7 +31589,7 @@
         <v>46131.360609965275</v>
       </c>
       <c r="D33" s="1">
-        <v>46131.61059027778</v>
+        <v>46131.36059027778</v>
       </c>
       <c r="E33">
         <v>35979</v>
@@ -31732,7 +31732,7 @@
         <v>46131.36097671296</v>
       </c>
       <c r="D34" s="1">
-        <v>46131.6109375</v>
+        <v>46131.3609375</v>
       </c>
       <c r="E34">
         <v>35117</v>
@@ -31875,7 +31875,7 @@
         <v>46131.361304502316</v>
       </c>
       <c r="D35" s="1">
-        <v>46131.611284722225</v>
+        <v>46131.361284722225</v>
       </c>
       <c r="E35">
         <v>34266</v>
@@ -32018,7 +32018,7 @@
         <v>46131.361651921296</v>
       </c>
       <c r="D36" s="1">
-        <v>46131.61163194444</v>
+        <v>46131.36163194444</v>
       </c>
       <c r="E36">
         <v>33410</v>
@@ -32161,7 +32161,7 @@
         <v>46131.361999050925</v>
       </c>
       <c r="D37" s="1">
-        <v>46131.611979166664</v>
+        <v>46131.361979166664</v>
       </c>
       <c r="E37">
         <v>32565</v>
@@ -32304,7 +32304,7 @@
         <v>46131.36234954861</v>
       </c>
       <c r="D38" s="1">
-        <v>46131.61232638889</v>
+        <v>46131.36232638889</v>
       </c>
       <c r="E38">
         <v>31751</v>
@@ -32447,7 +32447,7 @@
         <v>46131.36269405093</v>
       </c>
       <c r="D39" s="1">
-        <v>46131.61267361111</v>
+        <v>46131.36267361111</v>
       </c>
       <c r="E39">
         <v>30951</v>
@@ -32590,7 +32590,7 @@
         <v>46131.363040902776</v>
       </c>
       <c r="D40" s="1">
-        <v>46131.613020833334</v>
+        <v>46131.363020833334</v>
       </c>
       <c r="E40">
         <v>30146</v>
@@ -32733,7 +32733,7 @@
         <v>46131.36338791667</v>
       </c>
       <c r="D41" s="1">
-        <v>46131.61336805556</v>
+        <v>46131.36336805556</v>
       </c>
       <c r="E41">
         <v>29356</v>
@@ -32876,7 +32876,7 @@
         <v>46131.36373476852</v>
       </c>
       <c r="D42" s="1">
-        <v>46131.61371527778</v>
+        <v>46131.36371527778</v>
       </c>
       <c r="E42">
         <v>28583</v>
@@ -33019,7 +33019,7 @@
         <v>46131.364081921296</v>
       </c>
       <c r="D43" s="1">
-        <v>46131.6140625</v>
+        <v>46131.3640625</v>
       </c>
       <c r="E43">
         <v>27847</v>
@@ -33162,7 +33162,7 @@
         <v>46131.36442908565</v>
       </c>
       <c r="D44" s="1">
-        <v>46131.61440972222</v>
+        <v>46131.36440972222</v>
       </c>
       <c r="E44">
         <v>27105</v>
@@ -33305,7 +33305,7 @@
         <v>46131.36477721065</v>
       </c>
       <c r="D45" s="1">
-        <v>46131.614756944444</v>
+        <v>46131.364756944444</v>
       </c>
       <c r="E45">
         <v>26406</v>
@@ -33448,7 +33448,7 @@
         <v>46131.36512768519</v>
       </c>
       <c r="D46" s="1">
-        <v>46131.61510416667</v>
+        <v>46131.36510416667</v>
       </c>
       <c r="E46">
         <v>25717</v>
@@ -33591,7 +33591,7 @@
         <v>46131.365475833336</v>
       </c>
       <c r="D47" s="1">
-        <v>46131.61545138889</v>
+        <v>46131.36545138889</v>
       </c>
       <c r="E47">
         <v>25032</v>
@@ -33734,7 +33734,7 @@
         <v>46131.36581888889</v>
       </c>
       <c r="D48" s="1">
-        <v>46131.615798611114</v>
+        <v>46131.365798611114</v>
       </c>
       <c r="E48">
         <v>24364</v>
@@ -33877,7 +33877,7 @@
         <v>46131.366166134256</v>
       </c>
       <c r="D49" s="1">
-        <v>46131.61614583333</v>
+        <v>46131.36614583333</v>
       </c>
       <c r="E49">
         <v>23710</v>
@@ -34020,7 +34020,7 @@
         <v>46131.36651597222</v>
       </c>
       <c r="D50" s="1">
-        <v>46131.61649305555</v>
+        <v>46131.36649305555</v>
       </c>
       <c r="E50">
         <v>23027</v>
@@ -34163,7 +34163,7 @@
         <v>46131.36686028935</v>
       </c>
       <c r="D51" s="1">
-        <v>46131.61684027778</v>
+        <v>46131.36684027778</v>
       </c>
       <c r="E51">
         <v>22351</v>
@@ -34306,7 +34306,7 @@
         <v>46131.367211377314</v>
       </c>
       <c r="D52" s="1">
-        <v>46131.6171875</v>
+        <v>46131.3671875</v>
       </c>
       <c r="E52">
         <v>21664</v>
@@ -34449,7 +34449,7 @@
         <v>46131.36755440972</v>
       </c>
       <c r="D53" s="1">
-        <v>46131.61753472222</v>
+        <v>46131.36753472222</v>
       </c>
       <c r="E53">
         <v>20957</v>
@@ -34592,7 +34592,7 @@
         <v>46131.36790334491</v>
       </c>
       <c r="D54" s="1">
-        <v>46131.61788194445</v>
+        <v>46131.36788194445</v>
       </c>
       <c r="E54">
         <v>20283</v>
@@ -34735,7 +34735,7 @@
         <v>46131.36825337963</v>
       </c>
       <c r="D55" s="1">
-        <v>46131.61822916667</v>
+        <v>46131.36822916667</v>
       </c>
       <c r="E55">
         <v>19630</v>
@@ -34878,7 +34878,7 @@
         <v>46131.368598229164</v>
       </c>
       <c r="D56" s="1">
-        <v>46131.618576388886</v>
+        <v>46131.368576388886</v>
       </c>
       <c r="E56">
         <v>18984</v>
@@ -35021,7 +35021,7 @@
         <v>46131.36894361111</v>
       </c>
       <c r="D57" s="1">
-        <v>46131.61892361111</v>
+        <v>46131.36892361111</v>
       </c>
       <c r="E57">
         <v>18355</v>
@@ -35164,7 +35164,7 @@
         <v>46131.3692906713</v>
       </c>
       <c r="D58" s="1">
-        <v>46131.61927083333</v>
+        <v>46131.36927083333</v>
       </c>
       <c r="E58">
         <v>17738</v>
@@ -35307,7 +35307,7 @@
         <v>46131.369641921294</v>
       </c>
       <c r="D59" s="1">
-        <v>46131.619618055556</v>
+        <v>46131.369618055556</v>
       </c>
       <c r="E59">
         <v>17143</v>
@@ -35450,7 +35450,7 @@
         <v>46131.36998501157</v>
       </c>
       <c r="D60" s="1">
-        <v>46131.61996527778</v>
+        <v>46131.36996527778</v>
       </c>
       <c r="E60">
         <v>16554</v>
@@ -35593,7 +35593,7 @@
         <v>46131.37033513889</v>
       </c>
       <c r="D61" s="1">
-        <v>46131.6203125</v>
+        <v>46131.3703125</v>
       </c>
       <c r="E61">
         <v>15975</v>
@@ -35736,7 +35736,7 @@
         <v>46131.37068313657</v>
       </c>
       <c r="D62" s="1">
-        <v>46131.62065972222</v>
+        <v>46131.37065972222</v>
       </c>
       <c r="E62">
         <v>15417</v>
@@ -35879,7 +35879,7 @@
         <v>46131.37102972222</v>
       </c>
       <c r="D63" s="1">
-        <v>46131.62100694444</v>
+        <v>46131.37100694444</v>
       </c>
       <c r="E63">
         <v>14868</v>
@@ -36022,7 +36022,7 @@
         <v>46131.37137715278</v>
       </c>
       <c r="D64" s="1">
-        <v>46131.621354166666</v>
+        <v>46131.371354166666</v>
       </c>
       <c r="E64">
         <v>14311</v>
@@ -36165,7 +36165,7 @@
         <v>46131.371723634256</v>
       </c>
       <c r="D65" s="1">
-        <v>46131.62170138889</v>
+        <v>46131.37170138889</v>
       </c>
       <c r="E65">
         <v>13732</v>
@@ -36308,7 +36308,7 @@
         <v>46131.37207162037</v>
       </c>
       <c r="D66" s="1">
-        <v>46131.62204861111</v>
+        <v>46131.37204861111</v>
       </c>
       <c r="E66">
         <v>13180</v>
@@ -36451,7 +36451,7 @@
         <v>46131.372418530096</v>
       </c>
       <c r="D67" s="1">
-        <v>46131.622395833336</v>
+        <v>46131.372395833336</v>
       </c>
       <c r="E67">
         <v>12629</v>
@@ -36594,7 +36594,7 @@
         <v>46131.372765671294</v>
       </c>
       <c r="D68" s="1">
-        <v>46131.62274305556</v>
+        <v>46131.37274305556</v>
       </c>
       <c r="E68">
         <v>12070</v>
@@ -36737,7 +36737,7 @@
         <v>46131.37311305555</v>
       </c>
       <c r="D69" s="1">
-        <v>46131.623090277775</v>
+        <v>46131.373090277775</v>
       </c>
       <c r="E69">
         <v>11516</v>
@@ -36880,7 +36880,7 @@
         <v>46131.37346405093</v>
       </c>
       <c r="D70" s="1">
-        <v>46131.6234375</v>
+        <v>46131.3734375</v>
       </c>
       <c r="E70">
         <v>10944</v>
@@ -37023,7 +37023,7 @@
         <v>46131.373811412035</v>
       </c>
       <c r="D71" s="1">
-        <v>46131.62378472222</v>
+        <v>46131.37378472222</v>
       </c>
       <c r="E71">
         <v>10367</v>
@@ -37166,7 +37166,7 @@
         <v>46131.37415458333</v>
       </c>
       <c r="D72" s="1">
-        <v>46131.624131944445</v>
+        <v>46131.374131944445</v>
       </c>
       <c r="E72">
         <v>9788</v>
@@ -37309,7 +37309,7 @@
         <v>46131.3745028125</v>
       </c>
       <c r="D73" s="1">
-        <v>46131.62447916667</v>
+        <v>46131.37447916667</v>
       </c>
       <c r="E73">
         <v>9211</v>
@@ -37452,7 +37452,7 @@
         <v>46131.37484925926</v>
       </c>
       <c r="D74" s="1">
-        <v>46131.62482638889</v>
+        <v>46131.37482638889</v>
       </c>
       <c r="E74">
         <v>8659</v>
@@ -37595,7 +37595,7 @@
         <v>46131.375200138886</v>
       </c>
       <c r="D75" s="1">
-        <v>46131.62517361111</v>
+        <v>46131.37517361111</v>
       </c>
       <c r="E75">
         <v>8105</v>
@@ -37738,7 +37738,7 @@
         <v>46131.375543773145</v>
       </c>
       <c r="D76" s="1">
-        <v>46131.62552083333</v>
+        <v>46131.37552083333</v>
       </c>
       <c r="E76">
         <v>7557</v>
@@ -37881,7 +37881,7 @@
         <v>46131.37589054398</v>
       </c>
       <c r="D77" s="1">
-        <v>46131.625868055555</v>
+        <v>46131.375868055555</v>
       </c>
       <c r="E77">
         <v>7015</v>
@@ -38024,7 +38024,7 @@
         <v>46131.376238240744</v>
       </c>
       <c r="D78" s="1">
-        <v>46131.62621527778</v>
+        <v>46131.37621527778</v>
       </c>
       <c r="E78">
         <v>6493</v>
@@ -38167,7 +38167,7 @@
         <v>46131.37658596065</v>
       </c>
       <c r="D79" s="1">
-        <v>46131.6265625</v>
+        <v>46131.3765625</v>
       </c>
       <c r="E79">
         <v>5977</v>
@@ -38310,7 +38310,7 @@
         <v>46131.376934050924</v>
       </c>
       <c r="D80" s="1">
-        <v>46131.626909722225</v>
+        <v>46131.376909722225</v>
       </c>
       <c r="E80">
         <v>5466</v>
@@ -38453,7 +38453,7 @@
         <v>46131.37762629629</v>
       </c>
       <c r="D81" s="1">
-        <v>46131.627604166664</v>
+        <v>46131.377604166664</v>
       </c>
       <c r="E81">
         <v>4468</v>
